--- a/vlookup, xlookup.xlsx
+++ b/vlookup, xlookup.xlsx
@@ -8,15 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chjit\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CBE6CFC-969C-457E-9029-F94C656B996D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FD935C3-8447-4CFA-B0FF-25D579A40A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2070CA7F-564D-4F33-AD9B-634AC0B5E6C1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{2070CA7F-564D-4F33-AD9B-634AC0B5E6C1}"/>
   </bookViews>
   <sheets>
     <sheet name="VLOOKUP" sheetId="1" r:id="rId1"/>
     <sheet name="XLOOKUP" sheetId="2" r:id="rId2"/>
+    <sheet name="PIVOTE GRAPH" sheetId="4" r:id="rId3"/>
+    <sheet name="PivotTable" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="4" r:id="rId5"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="41">
   <si>
     <t>Emp ID</t>
   </si>
@@ -110,6 +115,54 @@
   </si>
   <si>
     <t>Pencil</t>
+  </si>
+  <si>
+    <t>Sales Person</t>
+  </si>
+  <si>
+    <t>Customers</t>
+  </si>
+  <si>
+    <t>Net Sales</t>
+  </si>
+  <si>
+    <t>Profit / Loss</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>RAVI</t>
+  </si>
+  <si>
+    <t>ANU</t>
+  </si>
+  <si>
+    <t>KIRAN</t>
+  </si>
+  <si>
+    <t>PRIYA</t>
+  </si>
+  <si>
+    <t>LAPTOP</t>
+  </si>
+  <si>
+    <t>MOUSE</t>
+  </si>
+  <si>
+    <t>KEYBOARD</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Net Sales</t>
+  </si>
+  <si>
+    <t>Sum of Customers</t>
   </si>
 </sst>
 </file>
@@ -156,11 +209,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -177,6 +238,1431 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[vlookup, xlookup.xlsx]PIVOTE GRAPH!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PIVOTE GRAPH'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Net Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'PIVOTE GRAPH'!$A$4:$A$18</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="10"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>KEYBOARD</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>MOUSE</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>KEYBOARD</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>LAPTOP</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>MOUSE</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>LAPTOP</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>MOUSE</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>KEYBOARD</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>LAPTOP</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>MOUSE</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>ANU</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>KIRAN</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>PRIYA</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>RAVI</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PIVOTE GRAPH'!$B$4:$B$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5765-4AD4-92D3-1839F55C7027}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PIVOTE GRAPH'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Customers</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'PIVOTE GRAPH'!$A$4:$A$18</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="10"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>KEYBOARD</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>MOUSE</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>KEYBOARD</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>LAPTOP</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>MOUSE</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>LAPTOP</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>MOUSE</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>KEYBOARD</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>LAPTOP</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>MOUSE</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>ANU</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>KIRAN</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>PRIYA</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>RAVI</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PIVOTE GRAPH'!$C$4:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5765-4AD4-92D3-1839F55C7027}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1975434032"/>
+        <c:axId val="229218320"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1975434032"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="229218320"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="229218320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1975434032"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F210F24C-3295-B055-C1BA-58BE42347505}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="JITHENDER SAI" refreshedDate="46312.524455902778" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{5EE3001E-6E5B-4A16-8358-6F32A7A3EEEF}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E11" sheet="PivotTable"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Sales Person" numFmtId="0">
+      <sharedItems count="4">
+        <s v="RAVI"/>
+        <s v="ANU"/>
+        <s v="KIRAN"/>
+        <s v="PRIYA"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Customers" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4" maxValue="10"/>
+    </cacheField>
+    <cacheField name="Net Sales" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="800" maxValue="2000"/>
+    </cacheField>
+    <cacheField name="Profit / Loss" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="250" maxValue="700"/>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="3">
+        <s v="LAPTOP"/>
+        <s v="MOUSE"/>
+        <s v="KEYBOARD"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="10">
+  <r>
+    <x v="0"/>
+    <n v="8"/>
+    <n v="1200"/>
+    <n v="500"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="6"/>
+    <n v="1200"/>
+    <n v="350"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="900"/>
+    <n v="300"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="10"/>
+    <n v="2000"/>
+    <n v="700"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="7"/>
+    <n v="1400"/>
+    <n v="450"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="9"/>
+    <n v="1800"/>
+    <n v="600"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="4"/>
+    <n v="800"/>
+    <n v="250"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="6"/>
+    <n v="1300"/>
+    <n v="400"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="7"/>
+    <n v="1100"/>
+    <n v="350"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="8"/>
+    <n v="1600"/>
+    <n v="550"/>
+    <x v="2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB5E1514-62CA-463B-B478-91797CD56C02}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:C18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of Net Sales" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Customers" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -689,4 +2175,393 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA2D44AD-11AC-4950-B6ED-218B2912D1A7}">
+  <dimension ref="A3:C18"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="5">
+        <v>2600</v>
+      </c>
+      <c r="C4" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1400</v>
+      </c>
+      <c r="C5" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1200</v>
+      </c>
+      <c r="C6" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="5">
+        <v>4400</v>
+      </c>
+      <c r="C7" s="5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1600</v>
+      </c>
+      <c r="C8" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="5">
+        <v>2000</v>
+      </c>
+      <c r="C9" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="5">
+        <v>800</v>
+      </c>
+      <c r="C10" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="5">
+        <v>3100</v>
+      </c>
+      <c r="C11" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1300</v>
+      </c>
+      <c r="C12" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1800</v>
+      </c>
+      <c r="C13" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="5">
+        <v>3200</v>
+      </c>
+      <c r="C14" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5">
+        <v>900</v>
+      </c>
+      <c r="C15" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1200</v>
+      </c>
+      <c r="C16" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="5">
+        <v>1100</v>
+      </c>
+      <c r="C17" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5">
+        <v>13300</v>
+      </c>
+      <c r="C18" s="5">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80DBBBB-7783-40A5-8CBE-10D19D5619BB}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="17.88671875" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2">
+        <v>500</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>1200</v>
+      </c>
+      <c r="D3">
+        <v>350</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>900</v>
+      </c>
+      <c r="D4">
+        <v>300</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>2000</v>
+      </c>
+      <c r="D5">
+        <v>700</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>1400</v>
+      </c>
+      <c r="D6">
+        <v>450</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>1800</v>
+      </c>
+      <c r="D7">
+        <v>600</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>800</v>
+      </c>
+      <c r="D8">
+        <v>250</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>1300</v>
+      </c>
+      <c r="D9">
+        <v>400</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>1100</v>
+      </c>
+      <c r="D10">
+        <v>350</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>1600</v>
+      </c>
+      <c r="D11">
+        <v>550</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>